--- a/AAII_Financials/Yearly/WERN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/WERN_YR_FIN.xlsx
@@ -1008,10 +1008,10 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>51700</v>
+        <v>43900</v>
       </c>
       <c r="E14" s="3">
-        <v>-23300</v>
+        <v>-22800</v>
       </c>
       <c r="F14" s="3">
         <v>-44900</v>
@@ -1128,10 +1128,10 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2911100</v>
+        <v>2918900</v>
       </c>
       <c r="E17" s="3">
-        <v>2979400</v>
+        <v>2979000</v>
       </c>
       <c r="F17" s="3">
         <v>3152200</v>
@@ -1179,10 +1179,10 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>63300</v>
+        <v>55500</v>
       </c>
       <c r="E18" s="3">
-        <v>50800</v>
+        <v>51200</v>
       </c>
       <c r="F18" s="3">
         <v>131300</v>
@@ -1302,10 +1302,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>350700</v>
+        <v>342900</v>
       </c>
       <c r="E21" s="3">
-        <v>341900</v>
+        <v>342400</v>
       </c>
       <c r="F21" s="3">
         <v>429300</v>
